--- a/diseases/d103/2026-2029.xlsx
+++ b/diseases/d103/2026-2029.xlsx
@@ -5831,6 +5831,151 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D103</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>hemolytic-uremic-syndrome</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Hemolytic uremic syndrome</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D103</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Hemolytic uremic syndrome</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>溶血性尿毒症综合征</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5864,7 +6009,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -5947,7 +6092,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -5957,7 +6102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -6009,7 +6154,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d103/2026-2029.xlsx
+++ b/diseases/d103/2026-2029.xlsx
@@ -5976,6 +5976,151 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D103</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>hemolytic-uremic-syndrome</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Hemolytic uremic syndrome</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D103</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Hemolytic uremic syndrome</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>溶血性尿毒症综合征</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6009,7 +6154,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6237,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -6102,7 +6247,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -6154,7 +6299,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d103/2026-2029.xlsx
+++ b/diseases/d103/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3881,6 +3986,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4026,6 +4136,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4171,6 +4286,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4316,6 +4436,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4461,6 +4586,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4606,6 +4736,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4751,6 +4886,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4896,6 +5036,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5041,6 +5186,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5186,6 +5336,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5331,6 +5486,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5476,6 +5636,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5621,6 +5786,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5766,6 +5936,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5911,6 +6086,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6054,6 +6234,11 @@
       <c r="S38" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">

--- a/diseases/d103/2026-2029.xlsx
+++ b/diseases/d103/2026-2029.xlsx
@@ -918,9 +918,6 @@
       <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -1224,9 +1221,6 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -1377,9 +1371,6 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -1530,9 +1521,6 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -1836,9 +1824,6 @@
       <c r="O9" t="n">
         <v>3</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -2142,9 +2127,6 @@
       <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -2295,9 +2277,6 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -2448,9 +2427,6 @@
       <c r="O13" t="n">
         <v>2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -2754,9 +2730,6 @@
       <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -2907,9 +2880,6 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -3060,9 +3030,6 @@
       <c r="O17" t="n">
         <v>3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -3213,9 +3180,6 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -3366,9 +3330,6 @@
       <c r="O19" t="n">
         <v>3</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -3519,9 +3480,6 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -3672,9 +3630,6 @@
       <c r="O21" t="n">
         <v>5</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -6301,6 +6256,156 @@
         </is>
       </c>
       <c r="BC38" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D103</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>hemolytic-uremic-syndrome</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Hemolytic uremic syndrome</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D103</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Hemolytic uremic syndrome</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>溶血性尿毒症综合征</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -6339,7 +6444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6527,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -6432,7 +6537,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -6484,7 +6589,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d103/2026-2029.xlsx
+++ b/diseases/d103/2026-2029.xlsx
@@ -20734,13 +20734,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R141" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -24673,6 +24673,150 @@
         </is>
       </c>
       <c r="BC168" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D103</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>hemolytic-uremic-syndrome</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Hemolytic uremic syndrome</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D103</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Hemolytic uremic syndrome</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>溶血性尿毒症综合征</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" t="n">
+        <v>1</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0.001195539327995473</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+        </is>
+      </c>
+      <c r="AT169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
         <is>
           <t>official_webforms_csv_export</t>
         </is>
@@ -24711,7 +24855,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -24794,7 +24938,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
@@ -24804,7 +24948,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d103/2026-2029.xlsx
+++ b/diseases/d103/2026-2029.xlsx
@@ -20734,13 +20734,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R141" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -24601,13 +24601,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R168" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U168" t="inlineStr">
         <is>
@@ -24745,13 +24745,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R169" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U169" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d103/2026-2029.xlsx
+++ b/diseases/d103/2026-2029.xlsx
@@ -54274,13 +54274,13 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R290" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="S290" t="inlineStr">
         <is>
@@ -54433,10 +54433,10 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U291" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16">
